--- a/incident_report_forms/044_helicopter_crash_incident_form--incident_report_forms.xlsx
+++ b/incident_report_forms/044_helicopter_crash_incident_form--incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Time of Crash</t>
+          <t>Time Crash</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>aircraft_registration</t>
+          <t>aircraft_registration_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Aircraft Registration</t>
+          <t>Aircraft Registration 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,7 +934,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>incident_reported_by</t>
+          <t>incident_reported_by_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>incident_location</t>
+          <t>incident_location_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Incident Location 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>incident_description</t>
+          <t>incident_description_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1032,7 +1032,7 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1210,7 +1210,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>incident_reported_by_choices</t>
+          <t>incident_reported_by_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1227,7 +1227,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>incident_reported_by_choices</t>
+          <t>incident_reported_by_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1244,7 +1244,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>incident_reported_by_choices</t>
+          <t>incident_reported_by_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
